--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125229230</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125229230</v>
       </c>
       <c r="B2" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125715805</v>
       </c>
       <c r="B3" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>125715419</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>125715143</v>
       </c>
       <c r="B7" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>125715137</v>
       </c>
       <c r="B9" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>125715543</v>
       </c>
       <c r="B13" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125715805</v>
       </c>
       <c r="B3" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>125715419</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>125715143</v>
       </c>
       <c r="B7" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>125715137</v>
       </c>
       <c r="B9" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>125715543</v>
       </c>
       <c r="B13" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125715805</v>
       </c>
       <c r="B3" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>125715419</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>125715143</v>
       </c>
       <c r="B7" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>125715137</v>
       </c>
       <c r="B9" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>125715543</v>
       </c>
       <c r="B13" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125715805</v>
       </c>
       <c r="B3" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>125715419</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>125715143</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>125715137</v>
       </c>
       <c r="B9" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125715252</v>
+        <v>125715389</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,26 +1497,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Abborrhålet, Abborrhålet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497341</v>
+        <v>497308</v>
       </c>
       <c r="R10" t="n">
-        <v>6828535</v>
+        <v>6828557</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1575,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125715389</v>
+        <v>125715252</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,17 +1594,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Abborrhålet, Abborrhålet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497308</v>
+        <v>497341</v>
       </c>
       <c r="R11" t="n">
-        <v>6828557</v>
+        <v>6828535</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>125715543</v>
       </c>
       <c r="B13" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 24031-2025 artfynd.xlsx
+++ b/artfynd/A 24031-2025 artfynd.xlsx
@@ -885,7 +885,7 @@
         <v>125715191</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>125715247</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>125715308</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125715389</v>
+        <v>125715252</v>
       </c>
       <c r="B10" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,17 +1497,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Abborrhålet, Abborrhålet, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497308</v>
+        <v>497341</v>
       </c>
       <c r="R10" t="n">
-        <v>6828557</v>
+        <v>6828535</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1566,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125715252</v>
+        <v>125715389</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,26 +1603,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Abborrhålet, Abborrhålet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497341</v>
+        <v>497308</v>
       </c>
       <c r="R11" t="n">
-        <v>6828535</v>
+        <v>6828557</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1675,7 +1675,7 @@
         <v>125715243</v>
       </c>
       <c r="B12" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
